--- a/artfynd/A 32160-2024 artfynd.xlsx
+++ b/artfynd/A 32160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54268159</v>
+        <v>119162294</v>
       </c>
       <c r="B2" t="n">
-        <v>77575</v>
+        <v>78524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalsberget, Ång</t>
+          <t>Renhagaberget (Renhagaberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660922.4666651849</v>
+        <v>660875</v>
       </c>
       <c r="R2" t="n">
-        <v>6982840.847252845</v>
+        <v>6982755</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera granar i myrkant</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,31 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Torrgran i myrkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119162294</v>
+        <v>119167008</v>
       </c>
       <c r="B3" t="n">
-        <v>78524</v>
+        <v>56520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,41 +794,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Renhagaberget (Renhagaberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660875</v>
+        <v>660474</v>
       </c>
       <c r="R3" t="n">
-        <v>6982755</v>
+        <v>6982852</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119167008</v>
+        <v>119161406</v>
       </c>
       <c r="B4" t="n">
-        <v>56520</v>
+        <v>78593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,43 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Renhagaberget (Renhagaberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660474</v>
+        <v>660860</v>
       </c>
       <c r="R4" t="n">
-        <v>6982852</v>
+        <v>6982807</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119161406</v>
+        <v>119162214</v>
       </c>
       <c r="B5" t="n">
         <v>78593</v>
@@ -1053,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660860</v>
+        <v>660884</v>
       </c>
       <c r="R5" t="n">
-        <v>6982807</v>
+        <v>6982778</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119162467</v>
+        <v>119160385</v>
       </c>
       <c r="B6" t="n">
-        <v>78593</v>
+        <v>57324</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>637</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>660925</v>
+        <v>660766</v>
       </c>
       <c r="R6" t="n">
-        <v>6982858</v>
+        <v>6982850</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119162214</v>
+        <v>119166929</v>
       </c>
       <c r="B7" t="n">
-        <v>78593</v>
+        <v>91830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>637</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>660884</v>
+        <v>660582</v>
       </c>
       <c r="R7" t="n">
-        <v>6982778</v>
+        <v>6982828</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119160385</v>
+        <v>119160131</v>
       </c>
       <c r="B8" t="n">
-        <v>57324</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,13 +1347,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660766</v>
+        <v>660691</v>
       </c>
       <c r="R8" t="n">
-        <v>6982850</v>
+        <v>6982864</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119166929</v>
+        <v>119161897</v>
       </c>
       <c r="B9" t="n">
-        <v>91830</v>
+        <v>78593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660582</v>
+        <v>660894</v>
       </c>
       <c r="R9" t="n">
-        <v>6982828</v>
+        <v>6982783</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119160131</v>
+        <v>119160498</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>97822</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>660691</v>
+        <v>660769</v>
       </c>
       <c r="R10" t="n">
-        <v>6982864</v>
+        <v>6982842</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119161897</v>
+        <v>119162345</v>
       </c>
       <c r="B11" t="n">
-        <v>78593</v>
+        <v>78524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>660894</v>
+        <v>660858</v>
       </c>
       <c r="R11" t="n">
-        <v>6982783</v>
+        <v>6982733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119162756</v>
+        <v>119162319</v>
       </c>
       <c r="B12" t="n">
-        <v>78593</v>
+        <v>57461</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,41 +1732,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Renhagaberget (Renhagaberget), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>660916</v>
+        <v>660870</v>
       </c>
       <c r="R12" t="n">
-        <v>6982898</v>
+        <v>6982760</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119160498</v>
+        <v>119167181</v>
       </c>
       <c r="B13" t="n">
-        <v>97822</v>
+        <v>91830</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,25 +1839,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>660769</v>
+        <v>660440</v>
       </c>
       <c r="R13" t="n">
-        <v>6982842</v>
+        <v>6982949</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,526 +1926,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>119162643</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>637</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ringlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Renhagaberget (Renhagaberget), Ång</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>660919</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6982877</v>
-      </c>
-      <c r="S14" t="n">
-        <v>15</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>119162345</v>
-      </c>
-      <c r="B15" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Renhagaberget (Renhagaberget), Ång</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>660858</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6982733</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>119162319</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Renhagaberget (Renhagaberget), Ång</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>660870</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6982760</v>
-      </c>
-      <c r="S16" t="n">
-        <v>25</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>119162694</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>637</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ringlav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Renhagaberget (Renhagaberget), Ång</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>660923</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6982894</v>
-      </c>
-      <c r="S17" t="n">
-        <v>15</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>119167181</v>
-      </c>
-      <c r="B18" t="n">
-        <v>91830</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Renhagaberget (Renhagaberget), Ång</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>660440</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6982949</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32160-2024 artfynd.xlsx
+++ b/artfynd/A 32160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119161406</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119161897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119166929</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119167181</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119160131</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162294</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162345</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119160385</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119167008</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119167231</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162319</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,8 +2033,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119160498</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>